--- a/nr-doc-core-condition/ig/ValueSet-fr-core-vs-condition-code-allergie.xlsx
+++ b/nr-doc-core-condition/ig/ValueSet-fr-core-vs-condition-code-allergie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:47:40+00:00</t>
+    <t>2026-09-16T08:14:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
